--- a/USDA Reports/CBOT_Reports_History.xlsx
+++ b/USDA Reports/CBOT_Reports_History.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J50"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1141,6 +1141,34 @@
       <c r="I50" s="4" t="n"/>
       <c r="J50" s="4" t="n"/>
     </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>July 3-9, 2026</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>235.1</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" t="n">
+        <v>422.1</v>
+      </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="n">
+        <v>315</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="n">
+        <v>1588.3</v>
+      </c>
+      <c r="J51" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1152,7 +1180,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1607,6 +1635,25 @@
       <c r="E50" s="4" t="n"/>
       <c r="F50" s="4" t="n"/>
     </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>JUL 16, 2026</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>213.993</v>
+      </c>
+      <c r="C51" t="n">
+        <v>-46</v>
+      </c>
+      <c r="E51" t="n">
+        <v>1549.849</v>
+      </c>
+      <c r="F51" t="n">
+        <v>-0.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1618,7 +1665,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K50"/>
+  <dimension ref="A1:K51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2372,6 +2419,48 @@
       <c r="J50" s="4" t="n"/>
       <c r="K50" s="4" t="n"/>
     </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-07-20T12:00:00+0000</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>74% thu hoạch</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>N/A (Cuối vụ)</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>53% G/E</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>97% đã gieo trồng</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Mỹ: 0% | Argentina: 66% (2/3 tiến độ)</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>67% Good to Excellent</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2383,7 +2472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2829,6 +2918,25 @@
       <c r="D50" s="6" t="n"/>
       <c r="E50" s="4" t="n"/>
       <c r="F50" s="4" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-07-10T12:00:00+0000</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>722</v>
+      </c>
+      <c r="C51" t="n">
+        <v>272.84</v>
+      </c>
+      <c r="E51" t="n">
+        <v>1790</v>
+      </c>
+      <c r="F51" t="n">
+        <v>275.26</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/USDA Reports/CBOT_Reports_History.xlsx
+++ b/USDA Reports/CBOT_Reports_History.xlsx
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -934,8 +934,6 @@
       <c r="D29" t="n">
         <v>422.1</v>
       </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
       <c r="G29" t="n">
         <v>315</v>
       </c>
@@ -945,7 +943,34 @@
       <c r="I29" t="n">
         <v>1588.3</v>
       </c>
-      <c r="J29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>July 10-16, 2026</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>290</v>
+      </c>
+      <c r="C30" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="D30" t="n">
+        <v>210.6</v>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="n">
+        <v>332.7</v>
+      </c>
+      <c r="H30" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1786.4</v>
+      </c>
+      <c r="J30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/USDA Reports/CBOT_Reports_History.xlsx
+++ b/USDA Reports/CBOT_Reports_History.xlsx
@@ -959,8 +959,6 @@
       <c r="D30" t="n">
         <v>210.6</v>
       </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
       <c r="G30" t="n">
         <v>332.7</v>
       </c>
@@ -970,7 +968,6 @@
       <c r="I30" t="n">
         <v>1786.4</v>
       </c>
-      <c r="J30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -983,7 +980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1295,6 +1292,26 @@
       </c>
       <c r="F28" t="n">
         <v>-0.3</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>JUL 23, 2026</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>394.785</v>
+      </c>
+      <c r="C29" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="n">
+        <v>1488.028</v>
+      </c>
+      <c r="F29" t="n">
+        <v>-7.7</v>
       </c>
     </row>
   </sheetData>

--- a/USDA Reports/CBOT_Reports_History.xlsx
+++ b/USDA Reports/CBOT_Reports_History.xlsx
@@ -1306,7 +1306,6 @@
       <c r="C29" t="n">
         <v>71.8</v>
       </c>
-      <c r="D29" t="inlineStr"/>
       <c r="E29" t="n">
         <v>1488.028</v>
       </c>
@@ -1325,7 +1324,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K33"/>
+  <dimension ref="A1:K34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="7"/>
@@ -1928,6 +1927,51 @@
       <c r="K33" t="inlineStr">
         <is>
           <t>67% Good to Excellent</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-07-27T12:00:00+0000</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>81% thu hoạch</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>N/A (Cuối vụ)</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2% thu hoạch</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>53% G/E</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>97% đã gieo trồng</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Mỹ: 0% | Argentina: 66% (2/3 tiến độ)</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>63% Good to Excellent</t>
         </is>
       </c>
     </row>

--- a/USDA Reports/CBOT_Reports_History.xlsx
+++ b/USDA Reports/CBOT_Reports_History.xlsx
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -968,6 +968,59 @@
       <c r="I30" t="n">
         <v>1786.4</v>
       </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>July 17-23, 2026</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>285.2</v>
+      </c>
+      <c r="C31" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="D31" t="n">
+        <v>319.2</v>
+      </c>
+      <c r="G31" t="n">
+        <v>362.9</v>
+      </c>
+      <c r="H31" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1528.5</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>07/23/2026</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>285.2</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" t="n">
+        <v>319.2</v>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="n">
+        <v>362.9</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1528.5</v>
+      </c>
+      <c r="J32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1936,7 +1989,6 @@
           <t>2026-07-27T12:00:00+0000</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
           <t>81% thu hoạch</t>
@@ -1947,7 +1999,6 @@
           <t>N/A (Cuối vụ)</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
           <t>2% thu hoạch</t>
@@ -1958,7 +2009,6 @@
           <t>53% G/E</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>97% đã gieo trồng</t>

--- a/USDA Reports/CBOT_Reports_History.xlsx
+++ b/USDA Reports/CBOT_Reports_History.xlsx
@@ -1009,8 +1009,6 @@
       <c r="D32" t="n">
         <v>319.2</v>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
         <v>362.9</v>
       </c>
@@ -1020,7 +1018,6 @@
       <c r="I32" t="n">
         <v>1528.5</v>
       </c>
-      <c r="J32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1033,7 +1030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1364,6 +1361,26 @@
       </c>
       <c r="F29" t="n">
         <v>-7.7</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>JUL 30, 2026</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>335.313</v>
+      </c>
+      <c r="C30" t="n">
+        <v>-19.7</v>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="n">
+        <v>1884.68</v>
+      </c>
+      <c r="F30" t="n">
+        <v>22.9</v>
       </c>
     </row>
   </sheetData>

--- a/USDA Reports/CBOT_Reports_History.xlsx
+++ b/USDA Reports/CBOT_Reports_History.xlsx
@@ -1375,7 +1375,6 @@
       <c r="C30" t="n">
         <v>-19.7</v>
       </c>
-      <c r="D30" t="inlineStr"/>
       <c r="E30" t="n">
         <v>1884.68</v>
       </c>
@@ -1394,7 +1393,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:K35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="7"/>
@@ -2039,6 +2038,51 @@
       <c r="K34" t="inlineStr">
         <is>
           <t>63% Good to Excellent</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-08-03T12:00:00+0000</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>86% thu hoạch</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>N/A (Cuối vụ)</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>5% thu hoạch</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>55% G/E</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>97% đã gieo trồng</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Mỹ: 0% | Argentina: 66% (2/3 tiến độ)</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>61% Good to Excellent</t>
         </is>
       </c>
     </row>

--- a/USDA Reports/CBOT_Reports_History.xlsx
+++ b/USDA Reports/CBOT_Reports_History.xlsx
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1018,6 +1018,34 @@
       <c r="I32" t="n">
         <v>1528.5</v>
       </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>07/30/2026</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>296.4</v>
+      </c>
+      <c r="C33" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D33" t="n">
+        <v>419</v>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="n">
+        <v>116.7</v>
+      </c>
+      <c r="H33" t="n">
+        <v>-67.8</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1925.5</v>
+      </c>
+      <c r="J33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2047,7 +2075,6 @@
           <t>2026-08-03T12:00:00+0000</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
           <t>86% thu hoạch</t>
@@ -2058,7 +2085,6 @@
           <t>N/A (Cuối vụ)</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
           <t>5% thu hoạch</t>
@@ -2069,7 +2095,6 @@
           <t>55% G/E</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>97% đã gieo trồng</t>

--- a/USDA Reports/CBOT_Reports_History.xlsx
+++ b/USDA Reports/CBOT_Reports_History.xlsx
@@ -1034,8 +1034,6 @@
       <c r="D33" t="n">
         <v>419</v>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
         <v>116.7</v>
       </c>
@@ -1045,7 +1043,6 @@
       <c r="I33" t="n">
         <v>1925.5</v>
       </c>
-      <c r="J33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1058,7 +1055,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1410,6 +1407,26 @@
         <v>22.9</v>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>AUG 06, 2026</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>421.277</v>
+      </c>
+      <c r="C31" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="n">
+        <v>1740.119</v>
+      </c>
+      <c r="F31" t="n">
+        <v>-7.8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1421,7 +1438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K35"/>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="7"/>
@@ -2106,6 +2123,48 @@
         </is>
       </c>
       <c r="K35" t="inlineStr">
+        <is>
+          <t>61% Good to Excellent</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-08-10T12:00:00+0000</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>91% thu hoạch</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>N/A (Cuối vụ)</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>24% thu hoạch</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>51% G/E</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>97% đã gieo trồng</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Mỹ: 0% | Argentina: 66% (2/3 tiến độ)</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
         <is>
           <t>61% Good to Excellent</t>
         </is>

--- a/USDA Reports/CBOT_Reports_History.xlsx
+++ b/USDA Reports/CBOT_Reports_History.xlsx
@@ -1419,7 +1419,6 @@
       <c r="C31" t="n">
         <v>24.4</v>
       </c>
-      <c r="D31" t="inlineStr"/>
       <c r="E31" t="n">
         <v>1740.119</v>
       </c>
@@ -2181,7 +2180,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2463,6 +2462,26 @@
       </c>
       <c r="F27" t="n">
         <v>275.26</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-08-12T12:00:00+0000</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>717</v>
+      </c>
+      <c r="C28" t="n">
+        <v>273.25</v>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="n">
+        <v>1653</v>
+      </c>
+      <c r="F28" t="n">
+        <v>274.66</v>
       </c>
     </row>
   </sheetData>

--- a/USDA Reports/CBOT_Reports_History.xlsx
+++ b/USDA Reports/CBOT_Reports_History.xlsx
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1043,6 +1043,34 @@
       <c r="I33" t="n">
         <v>1925.5</v>
       </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>255.9</v>
+      </c>
+      <c r="C34" t="n">
+        <v>-13.7</v>
+      </c>
+      <c r="D34" t="n">
+        <v>490.6</v>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="n">
+        <v>410.7</v>
+      </c>
+      <c r="H34" t="n">
+        <v>251.9</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1767.3</v>
+      </c>
+      <c r="J34" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2476,7 +2504,6 @@
       <c r="C28" t="n">
         <v>273.25</v>
       </c>
-      <c r="D28" t="inlineStr"/>
       <c r="E28" t="n">
         <v>1653</v>
       </c>

--- a/USDA Reports/CBOT_Reports_History.xlsx
+++ b/USDA Reports/CBOT_Reports_History.xlsx
@@ -1059,8 +1059,6 @@
       <c r="D34" t="n">
         <v>490.6</v>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
         <v>410.7</v>
       </c>
@@ -1070,7 +1068,6 @@
       <c r="I34" t="n">
         <v>1767.3</v>
       </c>
-      <c r="J34" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1083,7 +1080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1454,6 +1451,26 @@
         <v>-7.8</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>AUG 13, 2026</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>493.401</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="n">
+        <v>1911</v>
+      </c>
+      <c r="F32" t="n">
+        <v>8.6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1465,7 +1482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="7"/>
@@ -2194,6 +2211,48 @@
       <c r="K36" t="inlineStr">
         <is>
           <t>61% Good to Excellent</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-08-17T12:00:00+0000</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>96% thu hoạch</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>N/A (Cuối vụ)</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>41% thu hoạch</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>52% G/E</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>97% đã gieo trồng</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Mỹ: 0% | Argentina: 66% (2/3 tiến độ)</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>60% Good to Excellent</t>
         </is>
       </c>
     </row>

--- a/USDA Reports/CBOT_Reports_History.xlsx
+++ b/USDA Reports/CBOT_Reports_History.xlsx
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:J35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1068,6 +1068,34 @@
       <c r="I34" t="n">
         <v>1767.3</v>
       </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>08/13/2026</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>393.7</v>
+      </c>
+      <c r="C35" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="D35" t="n">
+        <v>524.3</v>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="n">
+        <v>232.9</v>
+      </c>
+      <c r="H35" t="n">
+        <v>-43.3</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1975.5</v>
+      </c>
+      <c r="J35" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1463,7 +1491,6 @@
       <c r="C32" t="n">
         <v>1.5</v>
       </c>
-      <c r="D32" t="inlineStr"/>
       <c r="E32" t="n">
         <v>1911</v>
       </c>

--- a/USDA Reports/CBOT_Reports_History.xlsx
+++ b/USDA Reports/CBOT_Reports_History.xlsx
@@ -1084,8 +1084,6 @@
       <c r="D35" t="n">
         <v>524.3</v>
       </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
         <v>232.9</v>
       </c>
@@ -1095,7 +1093,6 @@
       <c r="I35" t="n">
         <v>1975.5</v>
       </c>
-      <c r="J35" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1108,7 +1105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1498,6 +1495,25 @@
         <v>8.6</v>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>AUG 20, 2026</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>425.668</v>
+      </c>
+      <c r="C33" t="n">
+        <v>-17.2</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1296.271</v>
+      </c>
+      <c r="F33" t="n">
+        <v>-33.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1509,7 +1525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:K38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="7"/>
@@ -2280,6 +2296,51 @@
       <c r="K37" t="inlineStr">
         <is>
           <t>60% Good to Excellent</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-08-24T12:00:00+0000</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>N/A (Cuối vụ)</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>62% thu hoạch</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>51% G/E</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>97% đã gieo trồng</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Mỹ: 0% | Argentina: 66% (2/3 tiến độ)</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>57% Good to Excellent</t>
         </is>
       </c>
     </row>

--- a/USDA Reports/CBOT_Reports_History.xlsx
+++ b/USDA Reports/CBOT_Reports_History.xlsx
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J35"/>
+  <dimension ref="A1:J36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1093,6 +1093,34 @@
       <c r="I35" t="n">
         <v>1975.5</v>
       </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>08/20/2026</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>402.5</v>
+      </c>
+      <c r="C36" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="D36" t="n">
+        <v>427.8</v>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="H36" t="n">
+        <v>-86.59999999999999</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1458.7</v>
+      </c>
+      <c r="J36" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2305,7 +2333,6 @@
           <t>2026-08-24T12:00:00+0000</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -2316,7 +2343,6 @@
           <t>N/A (Cuối vụ)</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
           <t>62% thu hoạch</t>
@@ -2327,7 +2353,6 @@
           <t>51% G/E</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
           <t>97% đã gieo trồng</t>

--- a/USDA Reports/CBOT_Reports_History.xlsx
+++ b/USDA Reports/CBOT_Reports_History.xlsx
@@ -1109,8 +1109,6 @@
       <c r="D36" t="n">
         <v>427.8</v>
       </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
         <v>31.2</v>
       </c>
@@ -1120,7 +1118,6 @@
       <c r="I36" t="n">
         <v>1458.7</v>
       </c>
-      <c r="J36" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1133,7 +1130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1542,6 +1539,26 @@
         <v>-33.3</v>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>AUG 27, 2026</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>430.925</v>
+      </c>
+      <c r="C34" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="n">
+        <v>1496.034</v>
+      </c>
+      <c r="F34" t="n">
+        <v>13.1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1553,7 +1570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K38"/>
+  <dimension ref="A1:K39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="7"/>
@@ -2364,6 +2381,48 @@
         </is>
       </c>
       <c r="K38" t="inlineStr">
+        <is>
+          <t>57% Good to Excellent</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-08-31T12:00:00+0000</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>N/A (Cuối vụ)</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>77% thu hoạch</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>97% đã gieo trồng</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Mỹ: 0% | Argentina: 66% (2/3 tiến độ)</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
         <is>
           <t>57% Good to Excellent</t>
         </is>

--- a/USDA Reports/CBOT_Reports_History.xlsx
+++ b/USDA Reports/CBOT_Reports_History.xlsx
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J36"/>
+  <dimension ref="A1:J37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1118,6 +1118,34 @@
       <c r="I36" t="n">
         <v>1458.7</v>
       </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>08/27/2026</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>313.5</v>
+      </c>
+      <c r="C37" t="n">
+        <v>-22.1</v>
+      </c>
+      <c r="D37" t="n">
+        <v>474.8</v>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="n">
+        <v>-829.6</v>
+      </c>
+      <c r="H37" t="n">
+        <v>-2759</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1570.2</v>
+      </c>
+      <c r="J37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1551,7 +1579,6 @@
       <c r="C34" t="n">
         <v>-0.4</v>
       </c>
-      <c r="D34" t="inlineStr"/>
       <c r="E34" t="n">
         <v>1496.034</v>
       </c>

--- a/USDA Reports/CBOT_Reports_History.xlsx
+++ b/USDA Reports/CBOT_Reports_History.xlsx
@@ -1134,8 +1134,6 @@
       <c r="D37" t="n">
         <v>474.8</v>
       </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
         <v>-829.6</v>
       </c>
@@ -1145,7 +1143,6 @@
       <c r="I37" t="n">
         <v>1570.2</v>
       </c>
-      <c r="J37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1158,7 +1155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1586,6 +1583,26 @@
         <v>13.1</v>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>SEP 03, 2026</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>342.733</v>
+      </c>
+      <c r="C35" t="n">
+        <v>-20.7</v>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="n">
+        <v>1662.496</v>
+      </c>
+      <c r="F35" t="n">
+        <v>10.9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1597,7 +1614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K39"/>
+  <dimension ref="A1:K40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="7"/>
@@ -2452,6 +2469,48 @@
       <c r="K39" t="inlineStr">
         <is>
           <t>57% Good to Excellent</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-09-08T12:00:00+0000</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>N/A (Cuối vụ)</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>86% thu hoạch</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>97% đã gieo trồng</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Mỹ: 0% | Argentina: 66% (2/3 tiến độ)</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>56% Good to Excellent</t>
         </is>
       </c>
     </row>

--- a/USDA Reports/CBOT_Reports_History.xlsx
+++ b/USDA Reports/CBOT_Reports_History.xlsx
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:J38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,34 @@
       <c r="I37" t="n">
         <v>1570.2</v>
       </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>09/03/2026</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>194.2</v>
+      </c>
+      <c r="C38" t="n">
+        <v>-38.1</v>
+      </c>
+      <c r="D38" t="n">
+        <v>493.6</v>
+      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="n">
+        <v>953.6</v>
+      </c>
+      <c r="H38" t="n">
+        <v>-214.9</v>
+      </c>
+      <c r="I38" t="n">
+        <v>194.8</v>
+      </c>
+      <c r="J38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1595,7 +1623,6 @@
       <c r="C35" t="n">
         <v>-20.7</v>
       </c>
-      <c r="D35" t="inlineStr"/>
       <c r="E35" t="n">
         <v>1662.496</v>
       </c>
